--- a/Dépenses/dépenses seb.xlsx
+++ b/Dépenses/dépenses seb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kheopst-my.sharepoint.com/personal/sebastien_dury_kheops_ch/Documents/PERSO/GN/2026/Dépenses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_AD4DB114E441178AC67DF47D5E92E3C8683EDF18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8248AB9D-33C2-4C4E-967C-A510E9AEC1CA}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_AD4DB114E441178AC67DF47D5E92E3C8683EDF18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2610B597-837C-4ECF-A4D0-4AEF452F7922}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4320" yWindow="4290" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>gn celtiana Krondaar 2026</t>
   </si>
   <si>
     <t xml:space="preserve">encre uv et tampon </t>
+  </si>
+  <si>
+    <t>Customes monstres marins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location camion </t>
+  </si>
+  <si>
+    <t>fumigènes vets (16)</t>
   </si>
 </sst>
 </file>
@@ -398,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C4:F7"/>
+  <dimension ref="C4:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="3:6" x14ac:dyDescent="0.25">
@@ -412,6 +421,30 @@
       </c>
       <c r="F7">
         <v>21.37</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>65.95</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>65.48</v>
       </c>
     </row>
   </sheetData>

--- a/Dépenses/dépenses seb.xlsx
+++ b/Dépenses/dépenses seb.xlsx
@@ -1,32 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kheopst-my.sharepoint.com/personal/sebastien_dury_kheops_ch/Documents/PERSO/GN/2026/Dépenses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_AD4DB114E441178AC67DF47D5E92E3C8683EDF18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2610B597-837C-4ECF-A4D0-4AEF452F7922}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_AD4DB114E441178AC67DF47D5E92E3C8683EDF18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{088BCB90-9CD8-41E1-ACE3-6B057763EF74}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4320" yWindow="4290" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="765" windowWidth="28800" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>gn celtiana Krondaar 2026</t>
   </si>
@@ -41,6 +52,9 @@
   </si>
   <si>
     <t>fumigènes vets (16)</t>
+  </si>
+  <si>
+    <t>tentures</t>
   </si>
 </sst>
 </file>
@@ -133,6 +147,50 @@
         <a:xfrm>
           <a:off x="1219200" y="952500"/>
           <a:ext cx="9107171" cy="4048690"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>313524</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>28095</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14D5D3A3-D84A-31A5-F48F-090D91A1F293}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="5715000"/>
+          <a:ext cx="6409524" cy="3838095"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -407,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C4:F10"/>
+  <dimension ref="C4:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="3:6" x14ac:dyDescent="0.25">
@@ -445,6 +503,20 @@
       </c>
       <c r="F10">
         <v>65.48</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>142.41999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <f>SUM(F7:F13)</f>
+        <v>545.22</v>
       </c>
     </row>
   </sheetData>
